--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0059.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0059.xlsx
@@ -14100,7 +14100,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female:Cô ấy} một mình đánh bại Cetus the Tidebreaker! Đẩy nó về nơi nó thuộc về! Thậm chí còn mạnh hơn cả Blazing Nightwalker!</t>
+          <t>{Male=He;Female=She} một mình đánh bại Cetus the Tidebreaker! Đẩy nó về nơi nó thuộc về! Thậm chí còn mạnh hơn cả Blazing Nightwalker!</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>{PlayerName}, có vẻ như ta phải rút lại lời vừa nói rồi.</t>
+          <t>{PlayerName}, có vẻ như tao phải rút lại lời vừa nói rồi.</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Ừ, cảm ơn nhé. Cậu vừa cứu ta đấy.</t>
+          <t>Ừ, cảm ơn nhé. Cậu vừa cứu tao đấy.</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đó là... kiểu hài hước mà ta không hiểu nổi.</t>
+          <t>Đó là... kiểu hài hước mà tao không hiểu nổi.</t>
         </is>
       </c>
     </row>
@@ -20990,7 +20990,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Lũ cậu là ai thế hả?!</t>
+          <t>Lũ mày là ai thế hả?!</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Colleen hả? Đúng là sếp nói không sai. Bọn cậu đúng là vô dụng đến thảm hại!</t>
+          <t>Colleen hả? Đúng là sếp nói không sai. Bọn mày đúng là vô dụng đến thảm hại!</t>
         </is>
       </c>
     </row>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Ta không biết...</t>
+          <t>Tao không biết...</t>
         </is>
       </c>
     </row>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Nhưng trước hết phải mở cái nắp này đã... Đập vỡ nó đi. Ta không muốn phí thời gian nữa.</t>
+          <t>Nhưng trước hết phải mở cái nắp này đã... Đập vỡ nó đi. Tao không muốn phí thời gian nữa.</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25345,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Yes...</t>
+          <t>Ừ...</t>
         </is>
       </c>
     </row>
@@ -27100,7 +27100,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Trước khi nói về luật lệ... hãy học cách đừng làm khó đời ta trước đã.</t>
+          <t>Trước khi nói về luật lệ... hãy học cách đừng làm khó đời tao trước đã.</t>
         </is>
       </c>
     </row>
@@ -29375,7 +29375,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Ê, đừng có chõ mũi vào chuyện của người ta. Bọn ta thuộc Black Alley đấy.</t>
+          <t>Ê, đừng có chõ mũi vào chuyện của người ta. Bọn tao thuộc Black Alley đấy.</t>
         </is>
       </c>
     </row>
@@ -29440,7 +29440,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Đồ ngốc! {Male=Hắn;Female=Cô ta} đứng thế như một cao thủ. Chúng ta phải di chuyển ngay!</t>
+          <t>Đồ ngốc! {Male=He's;Female=She's} đứng thế như một cao thủ. Chúng ta phải di chuyển ngay!</t>
         </is>
       </c>
     </row>
@@ -30025,7 +30025,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Chúng lảm nhảm về "con tin" với "đòn nghi binh", rồi xông vào tấn công ta.</t>
+          <t>Chúng lảm nhảm về "con tin" với "đòn nghi binh", rồi xông vào tấn công tao.</t>
         </is>
       </c>
     </row>
@@ -30610,7 +30610,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Chỉ có hai tên trộm thôi. Ta đã xử xong rồi. Ta đang định tự đưa chúng đến &lt;te href=800005&gt;Chamber of Discipline&lt;/te&gt; đây.</t>
+          <t>Chỉ có hai tên trộm thôi. Tao đã xử xong rồi. Tao đang định tự đưa chúng đến &lt;te href=800005&gt;Phòng Kỷ Luật&lt;/te&gt; đây.</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Còn {Male=hắn;Female=cô ta} thì sao?</t>
+          <t>Còn {Male=him;Female=her} thì sao?</t>
         </is>
       </c>
     </row>
@@ -31130,7 +31130,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Ừ, vậy thì cậu sẽ đi cùng ta đến Phòng Hội thôi.</t>
+          <t>Ừ, vậy thì cậu sẽ đi cùng tao đến Phòng Hội thôi.</t>
         </is>
       </c>
     </row>
